--- a/data/trans_bre/IP15-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP15-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 10,77</t>
+          <t>-9,54; 10,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 14,4</t>
+          <t>-6,31; 15,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 25,32</t>
+          <t>2,18; 26,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 29,15</t>
+          <t>-12,01; 29,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-35,55; 61,13</t>
+          <t>-33,12; 56,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,09; 92,43</t>
+          <t>-23,89; 90,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 301,55</t>
+          <t>5,94; 309,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-41,64; 157,55</t>
+          <t>-42,89; 161,13</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 5,22</t>
+          <t>-3,14; 5,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 3,31</t>
+          <t>-5,24; 3,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 3,98</t>
+          <t>-4,23; 3,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 18,6</t>
+          <t>-3,86; 16,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,42; 31,95</t>
+          <t>-15,8; 31,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,94; 18,47</t>
+          <t>-23,02; 17,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 25,26</t>
+          <t>-21,43; 24,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 85,65</t>
+          <t>-16,33; 78,48</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,41; -2,97</t>
+          <t>-16,88; -2,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 6,86</t>
+          <t>-8,6; 6,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 6,79</t>
+          <t>-5,38; 8,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 10,28</t>
+          <t>-6,57; 10,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-59,35; -15,06</t>
+          <t>-61,56; -15,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,36; 36,69</t>
+          <t>-32,18; 32,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-29,48; 53,77</t>
+          <t>-29,65; 66,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-21,14; 50,29</t>
+          <t>-21,76; 51,64</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 1,73</t>
+          <t>-4,85; 1,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 3,29</t>
+          <t>-3,98; 3,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 4,82</t>
+          <t>-1,8; 5,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 12,68</t>
+          <t>-2,12; 13,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 9,36</t>
+          <t>-22,44; 11,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-16,23; 17,29</t>
+          <t>-17,41; 18,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 32,24</t>
+          <t>-10,0; 35,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 54,44</t>
+          <t>-8,71; 59,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP15-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP15-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 10,56</t>
+          <t>-9,15; 10,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 15,19</t>
+          <t>-6,0; 15,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 26,27</t>
+          <t>2,0; 24,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 29,27</t>
+          <t>-11,65; 31,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-33,12; 56,45</t>
+          <t>-32,3; 62,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,89; 90,62</t>
+          <t>-23,17; 103,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,94; 309,29</t>
+          <t>8,74; 292,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-42,89; 161,13</t>
+          <t>-42,51; 164,89</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 5,11</t>
+          <t>-2,86; 5,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 3,39</t>
+          <t>-5,04; 3,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 3,95</t>
+          <t>-3,66; 3,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 16,05</t>
+          <t>-3,49; 17,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 31,71</t>
+          <t>-14,65; 33,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 17,47</t>
+          <t>-22,32; 19,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,43; 24,42</t>
+          <t>-19,15; 25,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 78,48</t>
+          <t>-14,57; 83,5</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,88; -2,99</t>
+          <t>-15,57; -2,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 6,2</t>
+          <t>-8,6; 5,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 8,11</t>
+          <t>-4,73; 7,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 10,74</t>
+          <t>-7,14; 10,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-61,56; -15,43</t>
+          <t>-60,81; -14,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,18; 32,71</t>
+          <t>-32,84; 30,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-29,65; 66,53</t>
+          <t>-25,5; 64,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-21,76; 51,64</t>
+          <t>-23,27; 51,78</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 1,96</t>
+          <t>-4,62; 2,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 3,45</t>
+          <t>-3,84; 3,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 5,2</t>
+          <t>-2,02; 4,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 13,47</t>
+          <t>-2,73; 13,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 11,05</t>
+          <t>-21,39; 12,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 18,08</t>
+          <t>-16,68; 18,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 35,2</t>
+          <t>-10,74; 29,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 59,93</t>
+          <t>-11,29; 58,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP15-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP15-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..)</t>
+          <t>Menores que consumieron algún tipo de medicamento en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,49</t>
+          <t>-3,22</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>-13,14%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 10,97</t>
+          <t>-10,29; 10,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 15,25</t>
+          <t>-7,2; 14,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 24,58</t>
+          <t>2,15; 25,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 31,96</t>
+          <t>-17,51; 11,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-32,3; 62,17</t>
+          <t>-35,55; 61,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,17; 103,8</t>
+          <t>-27,09; 92,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,74; 292,47</t>
+          <t>4,92; 301,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-42,51; 164,89</t>
+          <t>-53,2; 62,65</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,02</t>
+          <t>-1,24</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>-5,46%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 5,54</t>
+          <t>-2,89; 5,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 3,33</t>
+          <t>-5,16; 3,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 3,81</t>
+          <t>-3,83; 3,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 17,12</t>
+          <t>-6,16; 3,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 33,73</t>
+          <t>-14,42; 31,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 19,04</t>
+          <t>-22,94; 18,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,15; 25,3</t>
+          <t>-20,15; 25,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 83,5</t>
+          <t>-24,2; 16,48</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,48</t>
+          <t>1,42</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,57; -2,71</t>
+          <t>-15,41; -2,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 5,63</t>
+          <t>-8,6; 6,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 7,95</t>
+          <t>-5,38; 6,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 10,82</t>
+          <t>-7,25; 9,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-60,81; -14,11</t>
+          <t>-59,35; -15,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,84; 30,54</t>
+          <t>-32,36; 36,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-25,5; 64,85</t>
+          <t>-29,48; 53,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-23,27; 51,78</t>
+          <t>-24,07; 45,52</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,98</t>
+          <t>-0,77</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>-3,26%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 2,32</t>
+          <t>-4,81; 1,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 3,43</t>
+          <t>-3,82; 3,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 4,51</t>
+          <t>-1,48; 4,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 13,05</t>
+          <t>-4,79; 3,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,39; 12,81</t>
+          <t>-22,6; 9,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-16,68; 18,08</t>
+          <t>-16,23; 17,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 29,52</t>
+          <t>-8,09; 32,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 58,21</t>
+          <t>-18,65; 15,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP15-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP15-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3,96</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13,62</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,22</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,84%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>106,36%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-13,14%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.936831711644362</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.95842109900491</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>13.61968941290193</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-3.224045655249255</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.04016145851731463</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.1884254685438604</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1.063605122946379</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.1313947422445995</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-10,29; 10,77</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-7,2; 14,4</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2,15; 25,32</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-17,51; 11,3</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-35,55; 61,13</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-27,09; 92,43</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4,92; 301,55</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-53,2; 62,65</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-10.28629540174802</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.196436480610643</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>2.153090528585447</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-17.51480715160607</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.3555310179439307</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.2709060979053934</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>0.04915281828638805</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.5319585773884369</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>10.76541097255199</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>14.39830227097668</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>25.31740185644435</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>11.30215174610497</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.6113446350416607</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.9242634679933663</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>3.015544998140899</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.6265079794619781</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,02</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,92</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-4,51%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-5,46%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,89; 5,22</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,16; 3,31</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,83; 3,98</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-6,16; 3,49</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-14,42; 31,95</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-22,94; 18,47</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-20,15; 25,26</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-24,2; 16,48</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.017153029876802</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.9216622401818086</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.05071714195393762</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.240844495892535</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.05534157754548847</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.04510473391302523</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.002895029233519184</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.05462578150114313</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-9,35</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,27</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,27</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,42</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-41,91%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-5,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.887314509394697</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.159471088891517</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.827791012492834</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-6.163069829037402</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.1441570675486474</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.2293519782397703</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.2015300405335984</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.2420448278124664</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-15,41; -2,97</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-8,6; 6,86</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-5,38; 6,79</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-7,25; 9,38</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-59,35; -15,06</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-32,36; 36,69</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-29,48; 53,77</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-24,07; 45,52</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5.219725317363364</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.314625217064243</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.979310953877727</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.492654465356648</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.3194936334094116</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.184748267402454</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.2525576805169751</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.1647644751453696</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +819,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,43</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,55</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,77</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-7,23%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-1,62%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,34%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-3,26%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-9.345504450864004</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.273483469403056</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.273608483249247</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.419875068941107</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.41906840187992</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.05513728516724309</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.08271459213348209</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.0554584522293066</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,81; 1,73</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,82; 3,29</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,48; 4,82</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-4,79; 3,37</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-22,6; 9,36</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-16,23; 17,29</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-8,09; 32,24</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-18,65; 15,45</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-15.41358834574918</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-8.601888107867474</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.381213810810983</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-7.247093901026286</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.5934949305660382</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.3235566729947094</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.29478623873149</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.2406931054459978</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-2.973048690726819</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.86250555389223</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>6.793512238163059</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>9.377973450844266</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>-0.1506445008334913</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.3669054948452721</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.5377217292845284</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.4551731139190325</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.433857554294762</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.342494806392532</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.54513693779936</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.7686451841550007</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.07229478137330225</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.01622834805115358</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.09335851419593136</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.03262862004572321</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.811845747674748</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.815479888337129</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.476697057000417</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-4.78979573030193</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2260091593478478</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1622971430284122</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.08089991387708446</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.1865408223498978</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.727567300631935</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.285482525782714</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.817980716713777</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3.367113479071117</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.09362772909261668</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.172907277886533</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.3224405682661183</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.154540035108641</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1017,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
